--- a/salidas/empresas/QCOM.xlsx
+++ b/salidas/empresas/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>29.87618255615234</v>
+        <v>29.87618446350098</v>
       </c>
       <c r="C2" t="n">
         <v>47.95999908447266</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>29.43428421020508</v>
+        <v>29.43425559997559</v>
       </c>
       <c r="C3" t="n">
         <v>47.15999984741211</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.58754539489746</v>
+        <v>31.58754348754883</v>
       </c>
       <c r="C4" t="n">
         <v>50.61000061035156</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>32.04317092895508</v>
+        <v>32.04318237304688</v>
       </c>
       <c r="C5" t="n">
         <v>51.34000015258789</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29202270507812</v>
+        <v>28.29202842712402</v>
       </c>
       <c r="C6" t="n">
         <v>45.20999908447266</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.07545471191406</v>
+        <v>25.0754566192627</v>
       </c>
       <c r="C7" t="n">
         <v>40.06999969482422</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>22.06540298461914</v>
+        <v>22.06540489196777</v>
       </c>
       <c r="C8" t="n">
         <v>35.2599983215332</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>23.64922142028809</v>
+        <v>23.64921760559082</v>
       </c>
       <c r="C9" t="n">
         <v>37.66999816894531</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>22.82052230834961</v>
+        <v>22.82051467895508</v>
       </c>
       <c r="C10" t="n">
         <v>36.34999847412109</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>22.84563255310059</v>
+        <v>22.84562683105469</v>
       </c>
       <c r="C11" t="n">
         <v>36.38999938964844</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>22.9711971282959</v>
+        <v>22.97120094299316</v>
       </c>
       <c r="C12" t="n">
         <v>36.59000015258789</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>23.80072212219238</v>
+        <v>23.80071258544922</v>
       </c>
       <c r="C13" t="n">
         <v>37.79000091552734</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>23.71883773803711</v>
+        <v>23.71884155273438</v>
       </c>
       <c r="C14" t="n">
         <v>37.65999984741211</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.45745086669922</v>
+        <v>25.45745658874512</v>
       </c>
       <c r="C15" t="n">
         <v>40.29999923706055</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>26.94826316833496</v>
+        <v>26.94825172424316</v>
       </c>
       <c r="C16" t="n">
         <v>42.65999984741211</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.66839790344238</v>
+        <v>27.66840362548828</v>
       </c>
       <c r="C17" t="n">
         <v>43.79999923706055</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>27.21751403808594</v>
+        <v>27.21750068664551</v>
       </c>
       <c r="C18" t="n">
         <v>42.95000076293945</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>27.49633026123047</v>
+        <v>27.49632835388184</v>
       </c>
       <c r="C19" t="n">
         <v>43.38999938964844</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>26.39369010925293</v>
+        <v>26.39368629455566</v>
       </c>
       <c r="C20" t="n">
         <v>41.65000152587891</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>25.37216186523438</v>
+        <v>25.37217712402344</v>
       </c>
       <c r="C21" t="n">
         <v>39.88999938964844</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>26.8796215057373</v>
+        <v>26.8796272277832</v>
       </c>
       <c r="C22" t="n">
         <v>42.2599983215332</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>27.17856597900391</v>
+        <v>27.17855453491211</v>
       </c>
       <c r="C23" t="n">
         <v>42.72999954223633</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>25.93825340270996</v>
+        <v>25.93825721740723</v>
       </c>
       <c r="C24" t="n">
         <v>40.77999877929688</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>25.11803817749023</v>
+        <v>25.11804962158203</v>
       </c>
       <c r="C25" t="n">
         <v>39.34999847412109</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>27.07768821716309</v>
+        <v>27.07770347595215</v>
       </c>
       <c r="C26" t="n">
         <v>42.41999816894531</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>27.14563941955566</v>
+        <v>27.14563751220703</v>
       </c>
       <c r="C27" t="n">
         <v>42.38999938964844</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>26.25550651550293</v>
+        <v>26.2555103302002</v>
       </c>
       <c r="C28" t="n">
         <v>41</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>27.65793609619141</v>
+        <v>27.65793037414551</v>
       </c>
       <c r="C29" t="n">
         <v>43.18999862670898</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>31.18611335754395</v>
+        <v>31.18610000610352</v>
       </c>
       <c r="C30" t="n">
         <v>48.54000091552734</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>35.55499649047852</v>
+        <v>35.55498886108398</v>
       </c>
       <c r="C32" t="n">
         <v>55.34000015258789</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>33.92818832397461</v>
+        <v>33.92819213867188</v>
       </c>
       <c r="C33" t="n">
         <v>52.65000152587891</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>27.69029808044434</v>
+        <v>27.69029235839844</v>
       </c>
       <c r="C34" t="n">
         <v>42.97000122070312</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>24.65512275695801</v>
+        <v>24.65513038635254</v>
       </c>
       <c r="C35" t="n">
         <v>38.2599983215332</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>21.63284111022949</v>
+        <v>21.63283538818359</v>
       </c>
       <c r="C36" t="n">
         <v>33.56999969482422</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>23.19990348815918</v>
+        <v>23.19991683959961</v>
       </c>
       <c r="C37" t="n">
         <v>35.83000183105469</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.3711109161377</v>
+        <v>22.37111663818359</v>
       </c>
       <c r="C38" t="n">
         <v>34.54999923706055</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>21.74678993225098</v>
+        <v>21.74679756164551</v>
       </c>
       <c r="C39" t="n">
         <v>33.43000030517578</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>25.31162643432617</v>
+        <v>25.3116283416748</v>
       </c>
       <c r="C40" t="n">
         <v>38.90999984741211</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>27.52988243103027</v>
+        <v>27.52989959716797</v>
       </c>
       <c r="C41" t="n">
         <v>42.31999969482422</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>28.46784400939941</v>
+        <v>28.46784782409668</v>
       </c>
       <c r="C42" t="n">
         <v>43.59000015258789</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>29.51931762695312</v>
+        <v>29.5192985534668</v>
       </c>
       <c r="C43" t="n">
         <v>45.20000076293945</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>30.17890930175781</v>
+        <v>30.17891502380371</v>
       </c>
       <c r="C44" t="n">
         <v>46.20999908447266</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>30.42612457275391</v>
+        <v>30.4261360168457</v>
       </c>
       <c r="C45" t="n">
         <v>46.41999816894531</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>29.48229026794434</v>
+        <v>29.48228645324707</v>
       </c>
       <c r="C46" t="n">
         <v>44.97999954223633</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.08989715576172</v>
+        <v>27.08989334106445</v>
       </c>
       <c r="C47" t="n">
         <v>41.33000183105469</v>
@@ -1380,7 +1392,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>30.43599510192871</v>
+        <v>30.43599319458008</v>
       </c>
       <c r="C49" t="n">
         <v>46.2599983215332</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>25.78439712524414</v>
+        <v>25.78441619873047</v>
       </c>
       <c r="C50" t="n">
         <v>39.18999862670898</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.23991203308105</v>
+        <v>24.23991584777832</v>
       </c>
       <c r="C51" t="n">
         <v>36.68000030517578</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>27.72918510437012</v>
+        <v>27.72919654846191</v>
       </c>
       <c r="C52" t="n">
         <v>41.95999908447266</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.56161880493164</v>
+        <v>25.56161689758301</v>
       </c>
       <c r="C53" t="n">
         <v>38.68000030517578</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>23.62581253051758</v>
+        <v>23.62582206726074</v>
       </c>
       <c r="C54" t="n">
         <v>35.56000137329102</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.81867408752441</v>
+        <v>21.81867218017578</v>
       </c>
       <c r="C55" t="n">
         <v>32.84000015258789</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>25.30009269714355</v>
+        <v>25.30010032653809</v>
       </c>
       <c r="C56" t="n">
         <v>38.08000183105469</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.57398414611816</v>
+        <v>25.57399559020996</v>
       </c>
       <c r="C57" t="n">
         <v>38.29999923706055</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>30.13459587097168</v>
+        <v>30.13457107543945</v>
       </c>
       <c r="C58" t="n">
         <v>45.13000106811523</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.15461730957031</v>
+        <v>30.15462684631348</v>
       </c>
       <c r="C59" t="n">
         <v>45.15999984741211</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>31.38737869262695</v>
+        <v>31.38738441467285</v>
       </c>
       <c r="C60" t="n">
         <v>46.81999969482422</v>
@@ -1709,11 +1721,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>33.17731094360352</v>
+        <v>33.17729949951172</v>
       </c>
       <c r="C61" t="n">
         <v>49.4900016784668</v>
@@ -1738,11 +1750,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>36.28789138793945</v>
+        <v>36.28790283203125</v>
       </c>
       <c r="C62" t="n">
         <v>54.13000106811523</v>
@@ -1767,11 +1779,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>40.07221221923828</v>
+        <v>40.07222366333008</v>
       </c>
       <c r="C63" t="n">
         <v>59.58000183105469</v>
@@ -1796,11 +1808,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>36.87745666503906</v>
+        <v>36.87746047973633</v>
       </c>
       <c r="C64" t="n">
         <v>54.83000183105469</v>
@@ -1825,11 +1837,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>38.39750289916992</v>
+        <v>38.39749526977539</v>
       </c>
       <c r="C65" t="n">
         <v>57.09000015258789</v>
@@ -1854,11 +1866,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>39.55739212036133</v>
+        <v>39.5573844909668</v>
       </c>
       <c r="C66" t="n">
         <v>58.59000015258789</v>
@@ -1883,11 +1895,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>38.34212112426758</v>
+        <v>38.34211730957031</v>
       </c>
       <c r="C67" t="n">
         <v>56.79000091552734</v>
@@ -1912,11 +1924,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.98505783081055</v>
+        <v>36.98505020141602</v>
       </c>
       <c r="C68" t="n">
         <v>54.77999877929688</v>
@@ -1941,11 +1953,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>34.89966583251953</v>
+        <v>34.89965438842773</v>
       </c>
       <c r="C69" t="n">
         <v>51.45999908447266</v>
@@ -1970,11 +1982,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>32.98038482666016</v>
+        <v>32.98039627075195</v>
       </c>
       <c r="C70" t="n">
         <v>48.63000106811523</v>
@@ -1999,11 +2011,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>34.99459838867188</v>
+        <v>34.99460220336914</v>
       </c>
       <c r="C71" t="n">
         <v>51.59999847412109</v>
@@ -2028,11 +2040,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>37.30890274047852</v>
+        <v>37.30890655517578</v>
       </c>
       <c r="C72" t="n">
         <v>54.79999923706055</v>
@@ -2057,11 +2069,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>37.24081802368164</v>
+        <v>37.24081420898438</v>
       </c>
       <c r="C73" t="n">
         <v>54.70000076293945</v>
@@ -2086,11 +2098,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>40.04579162597656</v>
+        <v>40.04579925537109</v>
       </c>
       <c r="C74" t="n">
         <v>58.81999969482422</v>
@@ -2115,11 +2127,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>42.47906494140625</v>
+        <v>42.47908020019531</v>
       </c>
       <c r="C75" t="n">
         <v>62.18000030517578</v>
@@ -2144,11 +2156,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.49605178833008</v>
+        <v>46.49604797363281</v>
       </c>
       <c r="C76" t="n">
         <v>68.05999755859375</v>
@@ -2173,11 +2185,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>43.60629653930664</v>
+        <v>43.60627365112305</v>
       </c>
       <c r="C77" t="n">
         <v>63.83000183105469</v>
@@ -2202,11 +2214,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>39.32043075561523</v>
+        <v>39.32041549682617</v>
       </c>
       <c r="C78" t="n">
         <v>57.31000137329102</v>
@@ -2231,11 +2243,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>38.20206451416016</v>
+        <v>38.20207214355469</v>
       </c>
       <c r="C79" t="n">
         <v>55.68000030517578</v>
@@ -2260,11 +2272,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>40.94647979736328</v>
+        <v>40.94646072387695</v>
       </c>
       <c r="C80" t="n">
         <v>59.68000030517578</v>
@@ -2289,11 +2301,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>42.167724609375</v>
+        <v>42.16771697998047</v>
       </c>
       <c r="C81" t="n">
         <v>61.45999908447266</v>
@@ -2318,11 +2330,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>43.0376091003418</v>
+        <v>43.03762435913086</v>
       </c>
       <c r="C82" t="n">
         <v>62.47000122070312</v>
@@ -2347,7 +2359,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2376,11 +2388,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>43.82989120483398</v>
+        <v>43.82987976074219</v>
       </c>
       <c r="C84" t="n">
         <v>63.61999893188477</v>
@@ -2405,11 +2417,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.7859001159668</v>
+        <v>42.78590393066406</v>
       </c>
       <c r="C85" t="n">
         <v>61.86000061035156</v>
@@ -2434,11 +2446,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>45.66319274902344</v>
+        <v>45.6631965637207</v>
       </c>
       <c r="C86" t="n">
         <v>66.01999664306641</v>
@@ -2463,11 +2475,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>45.40038299560547</v>
+        <v>45.40036773681641</v>
       </c>
       <c r="C87" t="n">
         <v>65.63999938964844</v>
@@ -2492,11 +2504,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>46.4704475402832</v>
+        <v>46.47043991088867</v>
       </c>
       <c r="C88" t="n">
         <v>66.94000244140625</v>
@@ -2521,11 +2533,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>42.76336288452148</v>
+        <v>42.76335906982422</v>
       </c>
       <c r="C89" t="n">
         <v>61.59999847412109</v>
@@ -2550,11 +2562,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.0684700012207</v>
+        <v>44.06847381591797</v>
       </c>
       <c r="C90" t="n">
         <v>63.47999954223633</v>
@@ -2579,11 +2591,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>42.64443206787109</v>
+        <v>42.64443969726562</v>
       </c>
       <c r="C91" t="n">
         <v>61.09000015258789</v>
@@ -2608,11 +2620,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>45.06669998168945</v>
+        <v>45.06670761108398</v>
       </c>
       <c r="C92" t="n">
         <v>64.55999755859375</v>
@@ -2637,11 +2649,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>46.51140213012695</v>
+        <v>46.51136779785156</v>
       </c>
       <c r="C93" t="n">
         <v>66.27999877929688</v>
@@ -2666,11 +2678,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>47.2411994934082</v>
+        <v>47.2412109375</v>
       </c>
       <c r="C94" t="n">
         <v>67.31999969482422</v>
@@ -2695,11 +2707,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>48.76398468017578</v>
+        <v>48.76396942138672</v>
       </c>
       <c r="C95" t="n">
         <v>69.48999786376953</v>
@@ -2724,11 +2736,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.88064575195312</v>
+        <v>51.88063812255859</v>
       </c>
       <c r="C96" t="n">
         <v>73.58000183105469</v>
@@ -2753,11 +2765,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>52.35305786132812</v>
+        <v>52.35306549072266</v>
       </c>
       <c r="C97" t="n">
         <v>74.25</v>
@@ -2782,11 +2794,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>52.33190155029297</v>
+        <v>52.3318977355957</v>
       </c>
       <c r="C98" t="n">
         <v>74.22000122070312</v>
@@ -2811,11 +2823,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>53.08635330200195</v>
+        <v>53.08634948730469</v>
       </c>
       <c r="C99" t="n">
         <v>75.29000091552734</v>
@@ -2840,7 +2852,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2869,11 +2881,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>55.75693893432617</v>
+        <v>55.75695419311523</v>
       </c>
       <c r="C101" t="n">
         <v>78.70999908447266</v>
@@ -2898,11 +2910,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>56.98956680297852</v>
+        <v>56.98954772949219</v>
       </c>
       <c r="C102" t="n">
         <v>80.44999694824219</v>
@@ -2927,11 +2939,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>56.39849090576172</v>
+        <v>56.39850234985352</v>
       </c>
       <c r="C103" t="n">
         <v>79.19999694824219</v>
@@ -2956,11 +2968,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>52.49618530273438</v>
+        <v>52.49617767333984</v>
       </c>
       <c r="C104" t="n">
         <v>73.72000122070312</v>
@@ -2985,11 +2997,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>54.49078369140625</v>
+        <v>54.49077606201172</v>
       </c>
       <c r="C105" t="n">
         <v>76.09999847412109</v>
@@ -3014,11 +3026,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>53.5384635925293</v>
+        <v>53.53844833374023</v>
       </c>
       <c r="C106" t="n">
         <v>74.76999664306641</v>
@@ -3043,11 +3055,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>56.21647644042969</v>
+        <v>56.21644973754883</v>
       </c>
       <c r="C107" t="n">
         <v>78.51000213623047</v>
@@ -3072,11 +3084,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.50457763671875</v>
+        <v>52.50457382202148</v>
       </c>
       <c r="C108" t="n">
         <v>72.90000152587891</v>
@@ -3101,11 +3113,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>53.53452682495117</v>
+        <v>53.53451538085938</v>
       </c>
       <c r="C109" t="n">
         <v>74.33000183105469</v>
@@ -3130,11 +3142,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>44.98541259765625</v>
+        <v>44.98539733886719</v>
       </c>
       <c r="C110" t="n">
         <v>62.45999908447266</v>
@@ -3159,11 +3171,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>52.22369003295898</v>
+        <v>52.22367477416992</v>
       </c>
       <c r="C111" t="n">
         <v>72.51000213623047</v>
@@ -3188,11 +3200,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>50.23152542114258</v>
+        <v>50.23150253295898</v>
       </c>
       <c r="C112" t="n">
         <v>69.33999633789062</v>
@@ -3217,11 +3229,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>49.26081085205078</v>
+        <v>49.26081466674805</v>
       </c>
       <c r="C113" t="n">
         <v>68</v>
@@ -3246,11 +3258,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>50.47783660888672</v>
+        <v>50.47780609130859</v>
       </c>
       <c r="C114" t="n">
         <v>69.68000030517578</v>
@@ -3275,11 +3287,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>45.68535232543945</v>
+        <v>45.68536758422852</v>
       </c>
       <c r="C115" t="n">
         <v>62.63000106811523</v>
@@ -3304,11 +3316,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>46.96919250488281</v>
+        <v>46.96917724609375</v>
       </c>
       <c r="C116" t="n">
         <v>64.38999938964844</v>
@@ -3333,11 +3345,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>41.61993789672852</v>
+        <v>41.61992645263672</v>
       </c>
       <c r="C117" t="n">
         <v>56.58000183105469</v>
@@ -3362,11 +3374,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>39.52349472045898</v>
+        <v>39.52347946166992</v>
       </c>
       <c r="C118" t="n">
         <v>53.72999954223633</v>
@@ -3391,11 +3403,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>43.70901870727539</v>
+        <v>43.70901489257812</v>
       </c>
       <c r="C119" t="n">
         <v>59.41999816894531</v>
@@ -3420,11 +3432,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>36.24396896362305</v>
+        <v>36.24397277832031</v>
       </c>
       <c r="C120" t="n">
         <v>48.79000091552734</v>
@@ -3449,11 +3461,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>37.13538360595703</v>
+        <v>37.13540649414062</v>
       </c>
       <c r="C121" t="n">
         <v>49.9900016784668</v>
@@ -3478,7 +3490,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3507,11 +3519,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>38.08382034301758</v>
+        <v>38.08381652832031</v>
       </c>
       <c r="C123" t="n">
         <v>50.79000091552734</v>
@@ -3536,11 +3548,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>38.34625625610352</v>
+        <v>38.34626388549805</v>
       </c>
       <c r="C124" t="n">
         <v>51.13999938964844</v>
@@ -3565,11 +3577,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>37.88136672973633</v>
+        <v>37.88136291503906</v>
       </c>
       <c r="C125" t="n">
         <v>50.52000045776367</v>
@@ -3594,7 +3606,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3623,11 +3635,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>40.55395126342773</v>
+        <v>40.55393981933594</v>
       </c>
       <c r="C127" t="n">
         <v>53.56999969482422</v>
@@ -3652,11 +3664,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>47.37476348876953</v>
+        <v>47.37475967407227</v>
       </c>
       <c r="C128" t="n">
         <v>62.58000183105469</v>
@@ -3681,7 +3693,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3710,11 +3722,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>52.29652786254883</v>
+        <v>52.2965202331543</v>
       </c>
       <c r="C130" t="n">
         <v>68.5</v>
@@ -3739,11 +3751,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>52.46446990966797</v>
+        <v>52.46448135375977</v>
       </c>
       <c r="C131" t="n">
         <v>68.72000122070312</v>
@@ -3768,11 +3780,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>52.42089080810547</v>
+        <v>52.42087554931641</v>
       </c>
       <c r="C132" t="n">
         <v>68.12999725341797</v>
@@ -3797,11 +3809,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>50.16646575927734</v>
+        <v>50.16647338867188</v>
       </c>
       <c r="C133" t="n">
         <v>65.19999694824219</v>
@@ -3826,11 +3838,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>41.1103401184082</v>
+        <v>41.11034774780273</v>
       </c>
       <c r="C134" t="n">
         <v>53.43000030517578</v>
@@ -3855,11 +3867,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>43.86337280273438</v>
+        <v>43.86336898803711</v>
       </c>
       <c r="C135" t="n">
         <v>56.47999954223633</v>
@@ -3884,7 +3896,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3913,11 +3925,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>41.73543930053711</v>
+        <v>41.73544692993164</v>
       </c>
       <c r="C137" t="n">
         <v>53.7400016784668</v>
@@ -3942,11 +3954,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>44.9149055480957</v>
+        <v>44.91490173339844</v>
       </c>
       <c r="C138" t="n">
         <v>57.27000045776367</v>
@@ -3971,11 +3983,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>43.30716705322266</v>
+        <v>43.30715942382812</v>
       </c>
       <c r="C139" t="n">
         <v>55.22000122070312</v>
@@ -4000,7 +4012,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4029,11 +4041,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>41.44764709472656</v>
+        <v>41.4476432800293</v>
       </c>
       <c r="C141" t="n">
         <v>52.27000045776367</v>
@@ -4058,11 +4070,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>41.10668182373047</v>
+        <v>41.1066780090332</v>
       </c>
       <c r="C142" t="n">
         <v>51.84000015258789</v>
@@ -4087,11 +4099,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>40.44852447509766</v>
+        <v>40.44852828979492</v>
       </c>
       <c r="C143" t="n">
         <v>51.0099983215332</v>
@@ -4116,11 +4128,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>53.04824829101562</v>
+        <v>53.04825973510742</v>
       </c>
       <c r="C144" t="n">
         <v>66.33999633789062</v>
@@ -4145,11 +4157,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>51.19307708740234</v>
+        <v>51.19307327270508</v>
       </c>
       <c r="C145" t="n">
         <v>64.01999664306641</v>
@@ -4174,11 +4186,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>54.5755500793457</v>
+        <v>54.57556533813477</v>
       </c>
       <c r="C146" t="n">
         <v>68.25</v>
@@ -4201,11 +4213,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>52.42284393310547</v>
+        <v>52.42283630371094</v>
       </c>
       <c r="C147" t="n">
         <v>65</v>
@@ -4228,11 +4240,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>44.68846130371094</v>
+        <v>44.6884651184082</v>
       </c>
       <c r="C148" t="n">
         <v>55.40999984741211</v>
@@ -4255,11 +4267,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>41.13982772827148</v>
+        <v>41.13983535766602</v>
       </c>
       <c r="C149" t="n">
         <v>51.0099983215332</v>
@@ -4282,11 +4294,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>47.36384201049805</v>
+        <v>47.36384963989258</v>
       </c>
       <c r="C150" t="n">
         <v>58.11999893188477</v>
@@ -4309,11 +4321,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>45.73398208618164</v>
+        <v>45.73397445678711</v>
       </c>
       <c r="C151" t="n">
         <v>56.11999893188477</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>52.22898864746094</v>
+        <v>52.2289924621582</v>
       </c>
       <c r="C152" t="n">
         <v>64.08999633789062</v>
@@ -4363,11 +4375,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>55.99397277832031</v>
+        <v>55.99398040771484</v>
       </c>
       <c r="C153" t="n">
         <v>68.70999908447266</v>
@@ -4390,11 +4402,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>59.23405075073242</v>
+        <v>59.23402786254883</v>
       </c>
       <c r="C154" t="n">
         <v>72.02999877929688</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>51.71773910522461</v>
+        <v>51.71773529052734</v>
       </c>
       <c r="C155" t="n">
         <v>62.88999938964844</v>
@@ -4444,11 +4456,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>47.91024780273438</v>
+        <v>47.91025543212891</v>
       </c>
       <c r="C156" t="n">
         <v>58.2599983215332</v>
@@ -4471,11 +4483,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>47.30814743041992</v>
+        <v>47.30815124511719</v>
       </c>
       <c r="C157" t="n">
         <v>56.90999984741211</v>
@@ -4498,7 +4510,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4527,11 +4539,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>44.38204193115234</v>
+        <v>44.38203430175781</v>
       </c>
       <c r="C159" t="n">
         <v>53.38999938964844</v>
@@ -4556,7 +4568,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4585,11 +4597,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>72.43067169189453</v>
+        <v>72.43068695068359</v>
       </c>
       <c r="C161" t="n">
         <v>86.12999725341797</v>
@@ -4614,11 +4626,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>56.1920166015625</v>
+        <v>56.19201278686523</v>
       </c>
       <c r="C162" t="n">
         <v>66.81999969482422</v>
@@ -4643,11 +4655,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>64.55548095703125</v>
+        <v>64.55549621582031</v>
       </c>
       <c r="C163" t="n">
         <v>76.06999969482422</v>
@@ -4672,11 +4684,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>62.08598327636719</v>
+        <v>62.08596801757812</v>
       </c>
       <c r="C164" t="n">
         <v>73.16000366210938</v>
@@ -4701,11 +4713,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>65.99815368652344</v>
+        <v>65.99816131591797</v>
       </c>
       <c r="C165" t="n">
         <v>77.76999664306641</v>
@@ -4730,11 +4742,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>65.24767303466797</v>
+        <v>65.24765777587891</v>
       </c>
       <c r="C166" t="n">
         <v>76.27999877929688</v>
@@ -4759,11 +4771,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>68.80599212646484</v>
+        <v>68.80599975585938</v>
       </c>
       <c r="C167" t="n">
         <v>80.44000244140625</v>
@@ -4788,11 +4800,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>71.46619415283203</v>
+        <v>71.46620941162109</v>
       </c>
       <c r="C168" t="n">
         <v>83.55000305175781</v>
@@ -4817,11 +4829,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>76.05451202392578</v>
+        <v>76.05451965332031</v>
       </c>
       <c r="C169" t="n">
         <v>88.23000335693359</v>
@@ -4846,7 +4858,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4875,11 +4887,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>67.49483489990234</v>
+        <v>67.49482727050781</v>
       </c>
       <c r="C171" t="n">
         <v>78.30000305175781</v>
@@ -4904,11 +4916,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>58.77837371826172</v>
+        <v>58.77838516235352</v>
       </c>
       <c r="C172" t="n">
         <v>67.65000152587891</v>
@@ -4933,11 +4945,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>68.35322570800781</v>
+        <v>68.35321807861328</v>
       </c>
       <c r="C173" t="n">
         <v>78.66999816894531</v>
@@ -4962,7 +4974,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4991,11 +5003,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>79.86210632324219</v>
+        <v>79.86207580566406</v>
       </c>
       <c r="C175" t="n">
         <v>91.20999908447266</v>
@@ -5020,7 +5032,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5049,11 +5061,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>104.2821731567383</v>
+        <v>104.2821578979492</v>
       </c>
       <c r="C177" t="n">
         <v>119.0999984741211</v>
@@ -5078,11 +5090,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>103.5906829833984</v>
+        <v>103.5906982421875</v>
       </c>
       <c r="C178" t="n">
         <v>117.6800003051758</v>
@@ -5107,11 +5119,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>108.5906753540039</v>
+        <v>108.5906600952148</v>
       </c>
       <c r="C179" t="n">
         <v>123.3600006103516</v>
@@ -5136,11 +5148,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>129.5499725341797</v>
+        <v>129.5499877929688</v>
       </c>
       <c r="C180" t="n">
         <v>147.1699981689453</v>
@@ -5165,11 +5177,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>134.6797790527344</v>
+        <v>134.6797943115234</v>
       </c>
       <c r="C181" t="n">
         <v>152.3399963378906</v>
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>138.1629943847656</v>
+        <v>138.1630249023438</v>
       </c>
       <c r="C182" t="n">
         <v>156.2799987792969</v>
@@ -5223,11 +5235,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>120.401969909668</v>
+        <v>120.4020080566406</v>
       </c>
       <c r="C183" t="n">
         <v>136.1900024414062</v>
@@ -5252,11 +5264,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>117.7779388427734</v>
+        <v>117.7779312133789</v>
       </c>
       <c r="C184" t="n">
         <v>132.5899963378906</v>
@@ -5281,11 +5293,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>123.2942123413086</v>
+        <v>123.2942047119141</v>
       </c>
       <c r="C185" t="n">
         <v>138.8000030517578</v>
@@ -5310,11 +5322,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>119.5100936889648</v>
+        <v>119.5101165771484</v>
       </c>
       <c r="C186" t="n">
         <v>134.5399932861328</v>
@@ -5339,11 +5351,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>127.6106872558594</v>
+        <v>127.6107330322266</v>
       </c>
       <c r="C187" t="n">
         <v>142.9299926757812</v>
@@ -5368,11 +5380,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>133.744384765625</v>
+        <v>133.7444152832031</v>
       </c>
       <c r="C188" t="n">
         <v>149.8000030517578</v>
@@ -5397,11 +5409,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>130.9676818847656</v>
+        <v>130.9677124023438</v>
       </c>
       <c r="C189" t="n">
         <v>146.6900024414062</v>
@@ -5426,11 +5438,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>115.6921768188477</v>
+        <v>115.6921844482422</v>
       </c>
       <c r="C190" t="n">
         <v>128.9799957275391</v>
@@ -5455,11 +5467,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>119.3339004516602</v>
+        <v>119.3338851928711</v>
       </c>
       <c r="C191" t="n">
         <v>133.0399932861328</v>
@@ -5484,7 +5496,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5513,11 +5525,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>164.6504058837891</v>
+        <v>164.6504211425781</v>
       </c>
       <c r="C193" t="n">
         <v>182.8699951171875</v>
@@ -5542,11 +5554,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>158.2487487792969</v>
+        <v>158.2487640380859</v>
       </c>
       <c r="C194" t="n">
         <v>175.7599945068359</v>
@@ -5571,11 +5583,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>154.8543701171875</v>
+        <v>154.8544006347656</v>
       </c>
       <c r="C195" t="n">
         <v>171.9900054931641</v>
@@ -5600,11 +5612,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>138.1682891845703</v>
+        <v>138.1683044433594</v>
       </c>
       <c r="C196" t="n">
         <v>152.8200073242188</v>
@@ -5629,11 +5641,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>126.2971496582031</v>
+        <v>126.297119140625</v>
       </c>
       <c r="C197" t="n">
         <v>139.6900024414062</v>
@@ -5658,11 +5670,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>129.4886779785156</v>
+        <v>129.4886932373047</v>
       </c>
       <c r="C198" t="n">
         <v>143.2200012207031</v>
@@ -5687,11 +5699,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>116.1008377075195</v>
+        <v>116.100830078125</v>
       </c>
       <c r="C199" t="n">
         <v>127.7399978637695</v>
@@ -5716,11 +5728,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>131.8426971435547</v>
+        <v>131.8427429199219</v>
       </c>
       <c r="C200" t="n">
         <v>145.0599975585938</v>
@@ -5745,11 +5757,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>120.8926849365234</v>
+        <v>120.8926696777344</v>
       </c>
       <c r="C201" t="n">
         <v>132.2700042724609</v>
@@ -5774,11 +5786,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>103.2619171142578</v>
+        <v>103.2619094848633</v>
       </c>
       <c r="C202" t="n">
         <v>112.9800033569336</v>
@@ -5803,11 +5815,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>107.5393524169922</v>
+        <v>107.5393600463867</v>
       </c>
       <c r="C203" t="n">
         <v>117.6600036621094</v>
@@ -5832,11 +5844,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>116.3469543457031</v>
+        <v>116.3469696044922</v>
       </c>
       <c r="C204" t="n">
         <v>126.4899978637695</v>
@@ -5861,11 +5873,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>101.1240921020508</v>
+        <v>101.1240692138672</v>
       </c>
       <c r="C205" t="n">
         <v>109.9400024414062</v>
@@ -5890,7 +5902,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5919,11 +5931,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>113.6243286132812</v>
+        <v>113.6243209838867</v>
       </c>
       <c r="C207" t="n">
         <v>123.5299987792969</v>
@@ -5948,11 +5960,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>118.0663681030273</v>
+        <v>118.0663757324219</v>
       </c>
       <c r="C208" t="n">
         <v>127.5800018310547</v>
@@ -5977,7 +5989,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6006,11 +6018,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>105.6818695068359</v>
+        <v>105.6818923950195</v>
       </c>
       <c r="C210" t="n">
         <v>113.4100036621094</v>
@@ -6035,7 +6047,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6064,11 +6076,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>123.1635131835938</v>
+        <v>123.1635055541992</v>
       </c>
       <c r="C212" t="n">
         <v>132.1699981689453</v>
@@ -6093,7 +6105,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6122,7 +6134,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6151,11 +6163,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>102.2822265625</v>
+        <v>102.2822113037109</v>
       </c>
       <c r="C215" t="n">
         <v>108.9899978637695</v>
@@ -6180,11 +6192,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>121.8778533935547</v>
+        <v>121.8778686523438</v>
       </c>
       <c r="C216" t="n">
         <v>129.0500030517578</v>
@@ -6209,11 +6221,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>136.5919799804688</v>
+        <v>136.5919494628906</v>
       </c>
       <c r="C217" t="n">
         <v>144.6300048828125</v>
@@ -6238,11 +6250,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>140.25634765625</v>
+        <v>140.2563323974609</v>
       </c>
       <c r="C218" t="n">
         <v>148.5099945068359</v>
@@ -6267,11 +6279,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>149.7775115966797</v>
+        <v>149.7774963378906</v>
       </c>
       <c r="C219" t="n">
         <v>157.7899932861328</v>
@@ -6296,11 +6308,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>160.7030334472656</v>
+        <v>160.7030487060547</v>
       </c>
       <c r="C220" t="n">
         <v>169.3000030517578</v>
@@ -6325,11 +6337,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>157.4282531738281</v>
+        <v>157.4282684326172</v>
       </c>
       <c r="C221" t="n">
         <v>165.8500061035156</v>
@@ -6354,11 +6366,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>194.4822235107422</v>
+        <v>194.4822387695312</v>
       </c>
       <c r="C222" t="n">
         <v>204.0500030517578</v>
@@ -6383,11 +6395,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>189.8405609130859</v>
+        <v>189.8405914306641</v>
       </c>
       <c r="C223" t="n">
         <v>199.1799926757812</v>
@@ -6412,7 +6424,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6441,11 +6453,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>167.0802917480469</v>
+        <v>167.0803070068359</v>
       </c>
       <c r="C225" t="n">
         <v>175.3000030517578</v>
@@ -6470,11 +6482,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>162.9140472412109</v>
+        <v>162.9140625</v>
       </c>
       <c r="C226" t="n">
         <v>170.0500030517578</v>
@@ -6499,11 +6511,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>155.9395446777344</v>
+        <v>155.9395599365234</v>
       </c>
       <c r="C227" t="n">
         <v>162.7700042724609</v>
@@ -6528,11 +6540,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>151.8774719238281</v>
+        <v>151.8774566650391</v>
       </c>
       <c r="C228" t="n">
         <v>158.5299987792969</v>
@@ -6557,11 +6569,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>147.9433746337891</v>
+        <v>147.9434051513672</v>
       </c>
       <c r="C229" t="n">
         <v>153.6199951171875</v>
@@ -6586,11 +6598,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>166.5398406982422</v>
+        <v>166.5398101806641</v>
       </c>
       <c r="C230" t="n">
         <v>172.9299926757812</v>
@@ -6615,11 +6627,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>151.3621826171875</v>
+        <v>151.3622131347656</v>
       </c>
       <c r="C231" t="n">
         <v>157.1699981689453</v>
@@ -6644,11 +6656,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>148.7314147949219</v>
+        <v>148.7314300537109</v>
       </c>
       <c r="C232" t="n">
         <v>153.6100006103516</v>
@@ -6673,11 +6685,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>143.7449798583984</v>
+        <v>143.7450103759766</v>
       </c>
       <c r="C233" t="n">
         <v>148.4600067138672</v>
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6731,7 +6743,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6760,11 +6772,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>142.9525756835938</v>
+        <v>142.9525604248047</v>
       </c>
       <c r="C236" t="n">
         <v>146.7599945068359</v>
@@ -6789,11 +6801,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>156.5601501464844</v>
+        <v>156.5601348876953</v>
       </c>
       <c r="C237" t="n">
         <v>160.7299957275391</v>
@@ -6818,7 +6830,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6847,11 +6859,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>177.2096099853516</v>
+        <v>177.2096252441406</v>
       </c>
       <c r="C239" t="n">
         <v>180.8999938964844</v>
@@ -6876,11 +6888,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>164.6609802246094</v>
+        <v>164.6609497070312</v>
       </c>
       <c r="C240" t="n">
         <v>168.0899963378906</v>
@@ -6905,11 +6917,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>168.416748046875</v>
+        <v>168.4167633056641</v>
       </c>
       <c r="C241" t="n">
         <v>171.0500030517578</v>
@@ -6934,7 +6946,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6963,7 +6975,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6992,11 +7004,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>127.6115798950195</v>
+        <v>127.611572265625</v>
       </c>
       <c r="C244" t="n">
         <v>128.7799987792969</v>
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7050,11 +7062,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>248.7424926757812</v>
+        <v>248.7425079345703</v>
       </c>
       <c r="C246" t="n">
         <v>251.0200042724609</v>
@@ -7079,7 +7091,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7108,7 +7120,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7137,7 +7149,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7166,32 +7178,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>197.2400054931641</v>
+        <v>194.2599945068359</v>
       </c>
       <c r="C250" t="n">
-        <v>197.2400054931641</v>
+        <v>194.2599945068359</v>
       </c>
       <c r="D250" t="n">
-        <v>243871200</v>
+        <v>252970200</v>
       </c>
       <c r="E250" t="n">
         <v>8.760000000000002</v>
       </c>
       <c r="F250" t="n">
-        <v>22.51598236223334</v>
+        <v>22.17579845968447</v>
       </c>
       <c r="G250" t="n">
         <v>1050000000</v>
       </c>
       <c r="H250" t="n">
-        <v>207102005767.8223</v>
+        <v>203972994232.1777</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2322582857142857</v>
+        <v>0.240924</v>
       </c>
     </row>
   </sheetData>
@@ -7223,75 +7235,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39628</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39720</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39810</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40205</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7369,13 +7381,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39811</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39901</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7411,13 +7423,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39902</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39992</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7453,13 +7465,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39993</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40083</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7486,7 +7498,7 @@
       <c r="I6" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="K6" t="n">
@@ -7499,13 +7511,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40084</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40174</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40205</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7532,7 +7544,7 @@
       <c r="I7" t="n">
         <v>1.24</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="K7" t="n">
@@ -7545,13 +7557,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40175</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40265</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7578,7 +7590,7 @@
       <c r="I8" t="n">
         <v>1.88</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="K8" t="n">
@@ -7591,13 +7603,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40266</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40356</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40380</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7624,7 +7636,7 @@
       <c r="I9" t="n">
         <v>1.91</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="K9" t="n">
@@ -7637,13 +7649,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40357</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40447</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7670,7 +7682,7 @@
       <c r="I10" t="n">
         <v>1.96</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="K10" t="n">
@@ -7683,13 +7695,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40448</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40538</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40569</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7716,7 +7728,7 @@
       <c r="I11" t="n">
         <v>2.17</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40569</v>
       </c>
       <c r="K11" t="n">
@@ -7729,13 +7741,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40539</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40629</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40653</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7762,7 +7774,7 @@
       <c r="I12" t="n">
         <v>2.3</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40653</v>
       </c>
       <c r="K12" t="n">
@@ -7775,13 +7787,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40630</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40720</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7808,7 +7820,7 @@
       <c r="I13" t="n">
         <v>2.44</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="K13" t="n">
@@ -7821,13 +7833,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40721</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40811</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7854,7 +7866,7 @@
       <c r="I14" t="n">
         <v>2.53</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="K14" t="n">
@@ -7867,13 +7879,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40812</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40902</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7900,7 +7912,7 @@
       <c r="I15" t="n">
         <v>2.63</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="K15" t="n">
@@ -7913,13 +7925,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40903</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40993</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41017</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7946,7 +7958,7 @@
       <c r="I16" t="n">
         <v>3.32</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41017</v>
       </c>
       <c r="K16" t="n">
@@ -7959,13 +7971,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40994</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41084</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41108</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7992,7 +8004,7 @@
       <c r="I17" t="n">
         <v>3.4</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41108</v>
       </c>
       <c r="K17" t="n">
@@ -8005,13 +8017,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41085</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8038,7 +8050,7 @@
       <c r="I18" t="n">
         <v>3.51</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K18" t="n">
@@ -8051,13 +8063,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41304</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8084,7 +8096,7 @@
       <c r="I19" t="n">
         <v>3.79</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41304</v>
       </c>
       <c r="K19" t="n">
@@ -8097,13 +8109,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8130,7 +8142,7 @@
       <c r="I20" t="n">
         <v>3.57</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="K20" t="n">
@@ -8143,13 +8155,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8176,7 +8188,7 @@
       <c r="I21" t="n">
         <v>3.78</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K21" t="n">
@@ -8189,13 +8201,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8222,7 +8234,7 @@
       <c r="I22" t="n">
         <v>3.91</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K22" t="n">
@@ -8235,13 +8247,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41637</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41668</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8268,7 +8280,7 @@
       <c r="I23" t="n">
         <v>3.91</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41668</v>
       </c>
       <c r="K23" t="n">
@@ -8281,13 +8293,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41638</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8314,7 +8326,7 @@
       <c r="I24" t="n">
         <v>3.989999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="K24" t="n">
@@ -8327,13 +8339,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8360,7 +8372,7 @@
       <c r="I25" t="n">
         <v>4.399999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="K25" t="n">
@@ -8373,13 +8385,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8406,7 +8418,7 @@
       <c r="I26" t="n">
         <v>4.65</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K26" t="n">
@@ -8419,13 +8431,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41911</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42032</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8452,7 +8464,7 @@
       <c r="I27" t="n">
         <v>4.73</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42032</v>
       </c>
       <c r="K27" t="n">
@@ -8465,13 +8477,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42002</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8498,7 +8510,7 @@
       <c r="I28" t="n">
         <v>4.220000000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="K28" t="n">
@@ -8511,13 +8523,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42093</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8544,7 +8556,7 @@
       <c r="I29" t="n">
         <v>3.64</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="K29" t="n">
@@ -8557,13 +8569,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42184</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8590,7 +8602,7 @@
       <c r="I30" t="n">
         <v>3.2</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K30" t="n">
@@ -8603,13 +8615,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42275</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42365</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8636,7 +8648,7 @@
       <c r="I31" t="n">
         <v>3.02</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="K31" t="n">
@@ -8649,13 +8661,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42366</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42456</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42480</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8682,7 +8694,7 @@
       <c r="I32" t="n">
         <v>3.17</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42480</v>
       </c>
       <c r="K32" t="n">
@@ -8695,13 +8707,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42457</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42547</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8728,7 +8740,7 @@
       <c r="I33" t="n">
         <v>3.41</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="K33" t="n">
@@ -8741,13 +8753,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42548</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42638</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8774,7 +8786,7 @@
       <c r="I34" t="n">
         <v>3.81</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K34" t="n">
@@ -8787,13 +8799,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42639</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42729</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42760</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8820,7 +8832,7 @@
       <c r="I35" t="n">
         <v>3.28</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42760</v>
       </c>
       <c r="K35" t="n">
@@ -8833,13 +8845,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42730</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42820</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42844</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8866,7 +8878,7 @@
       <c r="I36" t="n">
         <v>3</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42844</v>
       </c>
       <c r="K36" t="n">
@@ -8879,13 +8891,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42821</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42911</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42935</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8912,7 +8924,7 @@
       <c r="I37" t="n">
         <v>2.61</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42935</v>
       </c>
       <c r="K37" t="n">
@@ -8925,13 +8937,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42912</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43002</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8958,7 +8970,7 @@
       <c r="I38" t="n">
         <v>1.65</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K38" t="n">
@@ -8971,13 +8983,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43003</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43093</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9004,7 +9016,7 @@
       <c r="I39" t="n">
         <v>-2.84</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="K39" t="n">
@@ -9017,13 +9029,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43094</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43184</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9050,7 +9062,7 @@
       <c r="I40" t="n">
         <v>-3.1</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="K40" t="n">
@@ -9063,13 +9075,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43185</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43275</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9096,7 +9108,7 @@
       <c r="I41" t="n">
         <v>-2.86</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K41" t="n">
@@ -9109,13 +9121,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43276</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9142,7 +9154,7 @@
       <c r="I42" t="n">
         <v>-3.32</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K42" t="n">
@@ -9155,13 +9167,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43464</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9188,7 +9200,7 @@
       <c r="I43" t="n">
         <v>1.580000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="K43" t="n">
@@ -9201,13 +9213,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9234,7 +9246,7 @@
       <c r="I44" t="n">
         <v>1.890000000000001</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K44" t="n">
@@ -9247,13 +9259,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9280,7 +9292,7 @@
       <c r="I45" t="n">
         <v>2.820000000000001</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K45" t="n">
@@ -9293,13 +9305,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9326,7 +9338,7 @@
       <c r="I46" t="n">
         <v>3.590000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K46" t="n">
@@ -9339,13 +9351,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9372,7 +9384,7 @@
       <c r="I47" t="n">
         <v>3.52</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="K47" t="n">
@@ -9385,13 +9397,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43829</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9418,7 +9430,7 @@
       <c r="I48" t="n">
         <v>3.38</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K48" t="n">
@@ -9431,13 +9443,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43920</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9464,7 +9476,7 @@
       <c r="I49" t="n">
         <v>2.37</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K49" t="n">
@@ -9477,13 +9489,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44011</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9510,7 +9522,7 @@
       <c r="I50" t="n">
         <v>4.53</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="K50" t="n">
@@ -9523,13 +9535,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44102</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44192</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9556,7 +9568,7 @@
       <c r="I51" t="n">
         <v>5.850000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="K51" t="n">
@@ -9569,13 +9581,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44193</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44283</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9602,7 +9614,7 @@
       <c r="I52" t="n">
         <v>6.970000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K52" t="n">
@@ -9615,13 +9627,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44284</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44374</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9648,7 +9660,7 @@
       <c r="I53" t="n">
         <v>8</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K53" t="n">
@@ -9661,13 +9673,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44375</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44465</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9694,7 +9706,7 @@
       <c r="I54" t="n">
         <v>7.87</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K54" t="n">
@@ -9707,13 +9719,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44466</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44556</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9740,7 +9752,7 @@
       <c r="I55" t="n">
         <v>8.73</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="K55" t="n">
@@ -9753,13 +9765,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44557</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44647</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9786,7 +9798,7 @@
       <c r="I56" t="n">
         <v>9.77</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="K56" t="n">
@@ -9799,13 +9811,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44648</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44738</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9832,7 +9844,7 @@
       <c r="I57" t="n">
         <v>11.29</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K57" t="n">
@@ -9845,13 +9857,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44739</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44829</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9878,7 +9890,7 @@
       <c r="I58" t="n">
         <v>11.37</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K58" t="n">
@@ -9891,13 +9903,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44830</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44920</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9924,7 +9936,7 @@
       <c r="I59" t="n">
         <v>10.37</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="K59" t="n">
@@ -9937,13 +9949,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44921</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45011</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9970,7 +9982,7 @@
       <c r="I60" t="n">
         <v>9.32</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K60" t="n">
@@ -9983,13 +9995,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45012</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45102</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10016,7 +10028,7 @@
       <c r="I61" t="n">
         <v>7.629999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K61" t="n">
@@ -10029,13 +10041,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45103</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45193</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10062,7 +10074,7 @@
       <c r="I62" t="n">
         <v>6.42</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K62" t="n">
@@ -10075,13 +10087,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45284</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10108,7 +10120,7 @@
       <c r="I63" t="n">
         <v>6.9</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="K63" t="n">
@@ -10121,13 +10133,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45285</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45375</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10154,7 +10166,7 @@
       <c r="I64" t="n">
         <v>7.44</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K64" t="n">
@@ -10167,13 +10179,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45376</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45466</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10200,7 +10212,7 @@
       <c r="I65" t="n">
         <v>7.72</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K65" t="n">
@@ -10213,13 +10225,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45467</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10246,7 +10258,7 @@
       <c r="I66" t="n">
         <v>8.970000000000002</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="K66" t="n">
@@ -10259,13 +10271,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10292,7 +10304,7 @@
       <c r="I67" t="n">
         <v>9.34</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="K67" t="n">
@@ -10305,13 +10317,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45656</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10338,7 +10350,7 @@
       <c r="I68" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="K68" t="n">
@@ -10351,13 +10363,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10384,7 +10396,7 @@
       <c r="I69" t="n">
         <v>10.35</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="K69" t="n">
@@ -10397,13 +10409,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10430,7 +10442,7 @@
       <c r="I70" t="n">
         <v>5.010000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K70" t="n">
@@ -10443,13 +10455,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45929</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10476,7 +10488,7 @@
       <c r="I71" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="K71" t="n">
@@ -10489,13 +10501,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46020</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10522,7 +10534,7 @@
       <c r="I72" t="n">
         <v>9.32</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K72" t="n">
@@ -10535,13 +10547,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46111</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46201</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10568,7 +10580,7 @@
       <c r="I73" t="n">
         <v>8.760000000000002</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="K73" t="n">
@@ -10605,52 +10617,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40014</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="C2" t="n">
@@ -10679,10 +10691,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40119</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10711,10 +10723,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40203</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40205</v>
       </c>
       <c r="C4" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40287</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="C5" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40378</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40380</v>
       </c>
       <c r="C6" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C7" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40538</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40569</v>
       </c>
       <c r="C8" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40742</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="C9" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40938</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="C10" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41015</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41017</v>
       </c>
       <c r="C11" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41108</v>
       </c>
       <c r="C12" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41218</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C13" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41302</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41304</v>
       </c>
       <c r="C14" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41386</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="C15" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41477</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C16" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41582</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="C17" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41666</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41668</v>
       </c>
       <c r="C18" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41750</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="C19" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41841</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="C20" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41946</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C21" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42030</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42032</v>
       </c>
       <c r="C22" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42114</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="C23" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42205</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="C24" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42310</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C25" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42394</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="C26" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42478</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42480</v>
       </c>
       <c r="C27" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42569</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="C28" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="C29" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42758</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42760</v>
       </c>
       <c r="C30" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42842</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42844</v>
       </c>
       <c r="C31" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42933</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42935</v>
       </c>
       <c r="C32" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43038</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C33" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43129</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="C34" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43213</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="C35" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43304</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C36" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43409</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="C37" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43493</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="C38" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43584</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C39" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43675</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C40" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43773</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C41" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43864</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="C42" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C43" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C44" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44137</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="C45" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="C46" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44312</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C47" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44403</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C48" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C49" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="C50" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44676</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="C51" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44767</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C52" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C53" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="C54" t="n">
@@ -12343,10 +12355,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C55" t="n">
@@ -12375,10 +12387,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C56" t="n">
@@ -12407,10 +12419,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C57" t="n">
@@ -12439,10 +12451,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45320</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="C58" t="n">
@@ -12471,10 +12483,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C59" t="n">
@@ -12503,10 +12515,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C60" t="n">
@@ -12535,10 +12547,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45600</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C61" t="n">
@@ -12567,10 +12579,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45691</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="C62" t="n">
@@ -12599,10 +12611,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="C63" t="n">
@@ -12631,10 +12643,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45866</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="C64" t="n">
@@ -12663,10 +12675,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45964</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C65" t="n">
@@ -12695,10 +12707,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46055</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="C66" t="n">
@@ -12727,10 +12739,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C67" t="n">
@@ -12759,10 +12771,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46230</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="C68" t="n">
@@ -12809,12 +12821,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/QCOM.xlsx
+++ b/salidas/empresas/QCOM.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>29.87618446350098</v>
+        <v>29.87619590759277</v>
       </c>
       <c r="C2" t="n">
         <v>47.95999908447266</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>29.43425559997559</v>
+        <v>29.43427848815918</v>
       </c>
       <c r="C3" t="n">
         <v>47.15999984741211</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.58754348754883</v>
+        <v>31.58753776550293</v>
       </c>
       <c r="C4" t="n">
         <v>50.61000061035156</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>32.04318237304688</v>
+        <v>32.04317855834961</v>
       </c>
       <c r="C5" t="n">
         <v>51.34000015258789</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29202842712402</v>
+        <v>28.29203224182129</v>
       </c>
       <c r="C6" t="n">
         <v>45.20999908447266</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.0754566192627</v>
+        <v>25.07546234130859</v>
       </c>
       <c r="C7" t="n">
         <v>40.06999969482422</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>23.64921760559082</v>
+        <v>23.64921188354492</v>
       </c>
       <c r="C9" t="n">
         <v>37.66999816894531</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>22.82051467895508</v>
+        <v>22.82052993774414</v>
       </c>
       <c r="C10" t="n">
         <v>36.34999847412109</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>22.84562683105469</v>
+        <v>22.84562873840332</v>
       </c>
       <c r="C11" t="n">
         <v>36.38999938964844</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>22.97120094299316</v>
+        <v>22.97118759155273</v>
       </c>
       <c r="C12" t="n">
         <v>36.59000015258789</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.45745658874512</v>
+        <v>25.45744514465332</v>
       </c>
       <c r="C15" t="n">
         <v>40.29999923706055</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>26.94825172424316</v>
+        <v>26.94825744628906</v>
       </c>
       <c r="C16" t="n">
         <v>42.65999984741211</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.66840362548828</v>
+        <v>27.66838836669922</v>
       </c>
       <c r="C17" t="n">
         <v>43.79999923706055</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>27.21750068664551</v>
+        <v>27.21750259399414</v>
       </c>
       <c r="C18" t="n">
         <v>42.95000076293945</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>27.49632835388184</v>
+        <v>27.49631500244141</v>
       </c>
       <c r="C19" t="n">
         <v>43.38999938964844</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>26.39368629455566</v>
+        <v>26.39370346069336</v>
       </c>
       <c r="C20" t="n">
         <v>41.65000152587891</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>25.37217712402344</v>
+        <v>25.3721752166748</v>
       </c>
       <c r="C21" t="n">
         <v>39.88999938964844</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>26.8796272277832</v>
+        <v>26.87961959838867</v>
       </c>
       <c r="C22" t="n">
         <v>42.2599983215332</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>27.17855453491211</v>
+        <v>27.17856979370117</v>
       </c>
       <c r="C23" t="n">
         <v>42.72999954223633</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>25.11804962158203</v>
+        <v>25.11804580688477</v>
       </c>
       <c r="C25" t="n">
         <v>39.34999847412109</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>27.07770347595215</v>
+        <v>27.07771110534668</v>
       </c>
       <c r="C26" t="n">
         <v>42.41999816894531</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>27.14563751220703</v>
+        <v>27.1456356048584</v>
       </c>
       <c r="C27" t="n">
         <v>42.38999938964844</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>26.2555103302002</v>
+        <v>26.25550842285156</v>
       </c>
       <c r="C28" t="n">
         <v>41</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>27.65793037414551</v>
+        <v>27.65793418884277</v>
       </c>
       <c r="C29" t="n">
         <v>43.18999862670898</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>31.18610000610352</v>
+        <v>31.18610382080078</v>
       </c>
       <c r="C30" t="n">
         <v>48.54000091552734</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.50695419311523</v>
+        <v>28.50694465637207</v>
       </c>
       <c r="C31" t="n">
         <v>44.36999893188477</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>35.55498886108398</v>
+        <v>35.55499267578125</v>
       </c>
       <c r="C32" t="n">
         <v>55.34000015258789</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>33.92819213867188</v>
+        <v>33.92818450927734</v>
       </c>
       <c r="C33" t="n">
         <v>52.65000152587891</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>27.69029235839844</v>
+        <v>27.69028854370117</v>
       </c>
       <c r="C34" t="n">
         <v>42.97000122070312</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>24.65513038635254</v>
+        <v>24.65510749816895</v>
       </c>
       <c r="C35" t="n">
         <v>38.2599983215332</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>21.63283538818359</v>
+        <v>21.63284492492676</v>
       </c>
       <c r="C36" t="n">
         <v>33.56999969482422</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>23.19991683959961</v>
+        <v>23.19991874694824</v>
       </c>
       <c r="C37" t="n">
         <v>35.83000183105469</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.37111663818359</v>
+        <v>22.3711109161377</v>
       </c>
       <c r="C38" t="n">
         <v>34.54999923706055</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>21.74679756164551</v>
+        <v>21.74678993225098</v>
       </c>
       <c r="C39" t="n">
         <v>33.43000030517578</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>25.3116283416748</v>
+        <v>25.31163597106934</v>
       </c>
       <c r="C40" t="n">
         <v>38.90999984741211</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>27.52989959716797</v>
+        <v>27.52988624572754</v>
       </c>
       <c r="C41" t="n">
         <v>42.31999969482422</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>29.5192985534668</v>
+        <v>29.51930236816406</v>
       </c>
       <c r="C43" t="n">
         <v>45.20000076293945</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>30.17891502380371</v>
+        <v>30.17893028259277</v>
       </c>
       <c r="C44" t="n">
         <v>46.20999908447266</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>30.4261360168457</v>
+        <v>30.42614555358887</v>
       </c>
       <c r="C45" t="n">
         <v>46.41999816894531</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>29.48228645324707</v>
+        <v>29.4822826385498</v>
       </c>
       <c r="C46" t="n">
         <v>44.97999954223633</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.08989334106445</v>
+        <v>27.08987426757812</v>
       </c>
       <c r="C47" t="n">
         <v>41.33000183105469</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>29.60699462890625</v>
+        <v>29.60699844360352</v>
       </c>
       <c r="C48" t="n">
         <v>45</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>30.43599319458008</v>
+        <v>30.43599128723145</v>
       </c>
       <c r="C49" t="n">
         <v>46.2599983215332</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>25.78441619873047</v>
+        <v>25.78440093994141</v>
       </c>
       <c r="C50" t="n">
         <v>39.18999862670898</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.23991584777832</v>
+        <v>24.23991203308105</v>
       </c>
       <c r="C51" t="n">
         <v>36.68000030517578</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>27.72919654846191</v>
+        <v>27.72919273376465</v>
       </c>
       <c r="C52" t="n">
         <v>41.95999908447266</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.56161689758301</v>
+        <v>25.56160926818848</v>
       </c>
       <c r="C53" t="n">
         <v>38.68000030517578</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>23.62582206726074</v>
+        <v>23.62581634521484</v>
       </c>
       <c r="C54" t="n">
         <v>35.56000137329102</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>25.30010032653809</v>
+        <v>25.30009269714355</v>
       </c>
       <c r="C56" t="n">
         <v>38.08000183105469</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.57399559020996</v>
+        <v>25.57399749755859</v>
       </c>
       <c r="C57" t="n">
         <v>38.29999923706055</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>30.13457107543945</v>
+        <v>30.13458442687988</v>
       </c>
       <c r="C58" t="n">
         <v>45.13000106811523</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.15462684631348</v>
+        <v>30.15461158752441</v>
       </c>
       <c r="C59" t="n">
         <v>45.15999984741211</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>31.38738441467285</v>
+        <v>31.38739585876465</v>
       </c>
       <c r="C60" t="n">
         <v>46.81999969482422</v>
@@ -1725,7 +1725,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>33.17729949951172</v>
+        <v>33.17733001708984</v>
       </c>
       <c r="C61" t="n">
         <v>49.4900016784668</v>
@@ -1754,7 +1754,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>36.28790283203125</v>
+        <v>36.28788757324219</v>
       </c>
       <c r="C62" t="n">
         <v>54.13000106811523</v>
@@ -1783,7 +1783,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>40.07222366333008</v>
+        <v>40.07221984863281</v>
       </c>
       <c r="C63" t="n">
         <v>59.58000183105469</v>
@@ -1812,7 +1812,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>36.87746047973633</v>
+        <v>36.87746810913086</v>
       </c>
       <c r="C64" t="n">
         <v>54.83000183105469</v>
@@ -1841,7 +1841,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>38.39749526977539</v>
+        <v>38.39749145507812</v>
       </c>
       <c r="C65" t="n">
         <v>57.09000015258789</v>
@@ -1870,7 +1870,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>39.5573844909668</v>
+        <v>39.55741500854492</v>
       </c>
       <c r="C66" t="n">
         <v>58.59000015258789</v>
@@ -1899,7 +1899,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>38.34211730957031</v>
+        <v>38.34210205078125</v>
       </c>
       <c r="C67" t="n">
         <v>56.79000091552734</v>
@@ -1928,7 +1928,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.98505020141602</v>
+        <v>36.98505783081055</v>
       </c>
       <c r="C68" t="n">
         <v>54.77999877929688</v>
@@ -1957,7 +1957,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>34.89965438842773</v>
+        <v>34.89967727661133</v>
       </c>
       <c r="C69" t="n">
         <v>51.45999908447266</v>
@@ -1986,7 +1986,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>32.98039627075195</v>
+        <v>32.98038482666016</v>
       </c>
       <c r="C70" t="n">
         <v>48.63000106811523</v>
@@ -2015,7 +2015,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>34.99460220336914</v>
+        <v>34.99460983276367</v>
       </c>
       <c r="C71" t="n">
         <v>51.59999847412109</v>
@@ -2044,7 +2044,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>37.30890655517578</v>
+        <v>37.30889892578125</v>
       </c>
       <c r="C72" t="n">
         <v>54.79999923706055</v>
@@ -2073,7 +2073,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>37.24081420898438</v>
+        <v>37.24082183837891</v>
       </c>
       <c r="C73" t="n">
         <v>54.70000076293945</v>
@@ -2102,7 +2102,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>40.04579925537109</v>
+        <v>40.04581069946289</v>
       </c>
       <c r="C74" t="n">
         <v>58.81999969482422</v>
@@ -2131,7 +2131,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>42.47908020019531</v>
+        <v>42.47905731201172</v>
       </c>
       <c r="C75" t="n">
         <v>62.18000030517578</v>
@@ -2160,7 +2160,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.49604797363281</v>
+        <v>46.49605560302734</v>
       </c>
       <c r="C76" t="n">
         <v>68.05999755859375</v>
@@ -2189,7 +2189,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>43.60627365112305</v>
+        <v>43.60628128051758</v>
       </c>
       <c r="C77" t="n">
         <v>63.83000183105469</v>
@@ -2218,7 +2218,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>39.32041549682617</v>
+        <v>39.32041168212891</v>
       </c>
       <c r="C78" t="n">
         <v>57.31000137329102</v>
@@ -2247,7 +2247,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>38.20207214355469</v>
+        <v>38.20205688476562</v>
       </c>
       <c r="C79" t="n">
         <v>55.68000030517578</v>
@@ -2276,7 +2276,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>40.94646072387695</v>
+        <v>40.94646835327148</v>
       </c>
       <c r="C80" t="n">
         <v>59.68000030517578</v>
@@ -2305,7 +2305,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>42.16771697998047</v>
+        <v>42.16772842407227</v>
       </c>
       <c r="C81" t="n">
         <v>61.45999908447266</v>
@@ -2334,7 +2334,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>43.03762435913086</v>
+        <v>43.03762054443359</v>
       </c>
       <c r="C82" t="n">
         <v>62.47000122070312</v>
@@ -2392,7 +2392,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>43.82987976074219</v>
+        <v>43.82988739013672</v>
       </c>
       <c r="C84" t="n">
         <v>63.61999893188477</v>
@@ -2421,7 +2421,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.78590393066406</v>
+        <v>42.78589630126953</v>
       </c>
       <c r="C85" t="n">
         <v>61.86000061035156</v>
@@ -2450,7 +2450,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>45.6631965637207</v>
+        <v>45.66320037841797</v>
       </c>
       <c r="C86" t="n">
         <v>66.01999664306641</v>
@@ -2508,7 +2508,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>46.47043991088867</v>
+        <v>46.4704475402832</v>
       </c>
       <c r="C88" t="n">
         <v>66.94000244140625</v>
@@ -2537,7 +2537,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>42.76335906982422</v>
+        <v>42.76335144042969</v>
       </c>
       <c r="C89" t="n">
         <v>61.59999847412109</v>
@@ -2566,7 +2566,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.06847381591797</v>
+        <v>44.06848526000977</v>
       </c>
       <c r="C90" t="n">
         <v>63.47999954223633</v>
@@ -2595,7 +2595,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>42.64443969726562</v>
+        <v>42.64444351196289</v>
       </c>
       <c r="C91" t="n">
         <v>61.09000015258789</v>
@@ -2624,7 +2624,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>45.06670761108398</v>
+        <v>45.06669998168945</v>
       </c>
       <c r="C92" t="n">
         <v>64.55999755859375</v>
@@ -2653,7 +2653,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>46.51136779785156</v>
+        <v>46.51139068603516</v>
       </c>
       <c r="C93" t="n">
         <v>66.27999877929688</v>
@@ -2682,7 +2682,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>47.2412109375</v>
+        <v>47.24119186401367</v>
       </c>
       <c r="C94" t="n">
         <v>67.31999969482422</v>
@@ -2711,7 +2711,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>48.76396942138672</v>
+        <v>48.76397705078125</v>
       </c>
       <c r="C95" t="n">
         <v>69.48999786376953</v>
@@ -2740,7 +2740,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.88063812255859</v>
+        <v>51.88064193725586</v>
       </c>
       <c r="C96" t="n">
         <v>73.58000183105469</v>
@@ -2769,7 +2769,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>52.35306549072266</v>
+        <v>52.35304641723633</v>
       </c>
       <c r="C97" t="n">
         <v>74.25</v>
@@ -2798,7 +2798,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>52.3318977355957</v>
+        <v>52.33190536499023</v>
       </c>
       <c r="C98" t="n">
         <v>74.22000122070312</v>
@@ -2827,7 +2827,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>53.08634948730469</v>
+        <v>53.08634185791016</v>
       </c>
       <c r="C99" t="n">
         <v>75.29000091552734</v>
@@ -2856,7 +2856,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>55.86320877075195</v>
+        <v>55.86322402954102</v>
       </c>
       <c r="C100" t="n">
         <v>78.86000061035156</v>
@@ -2885,7 +2885,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>55.75695419311523</v>
+        <v>55.75696563720703</v>
       </c>
       <c r="C101" t="n">
         <v>78.70999908447266</v>
@@ -2914,7 +2914,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>56.98954772949219</v>
+        <v>56.98953247070312</v>
       </c>
       <c r="C102" t="n">
         <v>80.44999694824219</v>
@@ -2943,7 +2943,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>56.39850234985352</v>
+        <v>56.39850997924805</v>
       </c>
       <c r="C103" t="n">
         <v>79.19999694824219</v>
@@ -2972,7 +2972,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>52.49617767333984</v>
+        <v>52.4962043762207</v>
       </c>
       <c r="C104" t="n">
         <v>73.72000122070312</v>
@@ -3001,7 +3001,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>54.49077606201172</v>
+        <v>54.49078750610352</v>
       </c>
       <c r="C105" t="n">
         <v>76.09999847412109</v>
@@ -3030,7 +3030,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>53.53844833374023</v>
+        <v>53.53844451904297</v>
       </c>
       <c r="C106" t="n">
         <v>74.76999664306641</v>
@@ -3088,7 +3088,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.50457382202148</v>
+        <v>52.50458145141602</v>
       </c>
       <c r="C108" t="n">
         <v>72.90000152587891</v>
@@ -3117,7 +3117,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>53.53451538085938</v>
+        <v>53.53450393676758</v>
       </c>
       <c r="C109" t="n">
         <v>74.33000183105469</v>
@@ -3146,7 +3146,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>44.98539733886719</v>
+        <v>44.98540496826172</v>
       </c>
       <c r="C110" t="n">
         <v>62.45999908447266</v>
@@ -3175,7 +3175,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>52.22367477416992</v>
+        <v>52.22370529174805</v>
       </c>
       <c r="C111" t="n">
         <v>72.51000213623047</v>
@@ -3204,7 +3204,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>50.23150253295898</v>
+        <v>50.23153686523438</v>
       </c>
       <c r="C112" t="n">
         <v>69.33999633789062</v>
@@ -3233,7 +3233,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>49.26081466674805</v>
+        <v>49.26078796386719</v>
       </c>
       <c r="C113" t="n">
         <v>68</v>
@@ -3262,7 +3262,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>50.47780609130859</v>
+        <v>50.47782135009766</v>
       </c>
       <c r="C114" t="n">
         <v>69.68000030517578</v>
@@ -3291,7 +3291,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>45.68536758422852</v>
+        <v>45.68535995483398</v>
       </c>
       <c r="C115" t="n">
         <v>62.63000106811523</v>
@@ -3320,7 +3320,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>46.96917724609375</v>
+        <v>46.96917343139648</v>
       </c>
       <c r="C116" t="n">
         <v>64.38999938964844</v>
@@ -3349,7 +3349,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>41.61992645263672</v>
+        <v>41.61993026733398</v>
       </c>
       <c r="C117" t="n">
         <v>56.58000183105469</v>
@@ -3378,7 +3378,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>39.52347946166992</v>
+        <v>39.52348327636719</v>
       </c>
       <c r="C118" t="n">
         <v>53.72999954223633</v>
@@ -3407,7 +3407,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>43.70901489257812</v>
+        <v>43.70899963378906</v>
       </c>
       <c r="C119" t="n">
         <v>59.41999816894531</v>
@@ -3436,7 +3436,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>36.24397277832031</v>
+        <v>36.24396896362305</v>
       </c>
       <c r="C120" t="n">
         <v>48.79000091552734</v>
@@ -3465,7 +3465,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>37.13540649414062</v>
+        <v>37.13540267944336</v>
       </c>
       <c r="C121" t="n">
         <v>49.9900016784668</v>
@@ -3494,7 +3494,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>33.68110656738281</v>
+        <v>33.68112182617188</v>
       </c>
       <c r="C122" t="n">
         <v>45.34000015258789</v>
@@ -3552,7 +3552,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>38.34626388549805</v>
+        <v>38.34624099731445</v>
       </c>
       <c r="C124" t="n">
         <v>51.13999938964844</v>
@@ -3581,7 +3581,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>37.88136291503906</v>
+        <v>37.88135528564453</v>
       </c>
       <c r="C125" t="n">
         <v>50.52000045776367</v>
@@ -3610,7 +3610,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>41.575927734375</v>
+        <v>41.57593154907227</v>
       </c>
       <c r="C126" t="n">
         <v>54.91999816894531</v>
@@ -3668,7 +3668,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>47.37475967407227</v>
+        <v>47.3747673034668</v>
       </c>
       <c r="C128" t="n">
         <v>62.58000183105469</v>
@@ -3697,7 +3697,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>48.15097427368164</v>
+        <v>48.15096282958984</v>
       </c>
       <c r="C129" t="n">
         <v>63.06999969482422</v>
@@ -3755,7 +3755,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>52.46448135375977</v>
+        <v>52.4644775390625</v>
       </c>
       <c r="C131" t="n">
         <v>68.72000122070312</v>
@@ -3784,7 +3784,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>52.42087554931641</v>
+        <v>52.42088317871094</v>
       </c>
       <c r="C132" t="n">
         <v>68.12999725341797</v>
@@ -3813,7 +3813,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>50.16647338867188</v>
+        <v>50.16646575927734</v>
       </c>
       <c r="C133" t="n">
         <v>65.19999694824219</v>
@@ -3842,7 +3842,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>41.11034774780273</v>
+        <v>41.11034393310547</v>
       </c>
       <c r="C134" t="n">
         <v>53.43000030517578</v>
@@ -3900,7 +3900,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>44.53127288818359</v>
+        <v>44.5312614440918</v>
       </c>
       <c r="C136" t="n">
         <v>57.34000015258789</v>
@@ -3929,7 +3929,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>41.73544692993164</v>
+        <v>41.73543167114258</v>
       </c>
       <c r="C137" t="n">
         <v>53.7400016784668</v>
@@ -3958,7 +3958,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>44.91490173339844</v>
+        <v>44.9149055480957</v>
       </c>
       <c r="C138" t="n">
         <v>57.27000045776367</v>
@@ -3987,7 +3987,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>43.30715942382812</v>
+        <v>43.30716705322266</v>
       </c>
       <c r="C139" t="n">
         <v>55.22000122070312</v>
@@ -4016,7 +4016,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>41.71510314941406</v>
+        <v>41.7150993347168</v>
       </c>
       <c r="C140" t="n">
         <v>53.18999862670898</v>
@@ -4045,7 +4045,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>41.4476432800293</v>
+        <v>41.44765853881836</v>
       </c>
       <c r="C141" t="n">
         <v>52.27000045776367</v>
@@ -4074,7 +4074,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>41.1066780090332</v>
+        <v>41.10668182373047</v>
       </c>
       <c r="C142" t="n">
         <v>51.84000015258789</v>
@@ -4132,7 +4132,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>53.04825973510742</v>
+        <v>53.04826736450195</v>
       </c>
       <c r="C144" t="n">
         <v>66.33999633789062</v>
@@ -4161,7 +4161,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>51.19307327270508</v>
+        <v>51.19308090209961</v>
       </c>
       <c r="C145" t="n">
         <v>64.01999664306641</v>
@@ -4244,7 +4244,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>44.6884651184082</v>
+        <v>44.68845748901367</v>
       </c>
       <c r="C148" t="n">
         <v>55.40999984741211</v>
@@ -4271,7 +4271,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>41.13983535766602</v>
+        <v>41.13983154296875</v>
       </c>
       <c r="C149" t="n">
         <v>51.0099983215332</v>
@@ -4298,7 +4298,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>47.36384963989258</v>
+        <v>47.36384201049805</v>
       </c>
       <c r="C150" t="n">
         <v>58.11999893188477</v>
@@ -4325,7 +4325,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>45.73397445678711</v>
+        <v>45.73397827148438</v>
       </c>
       <c r="C151" t="n">
         <v>56.11999893188477</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>52.2289924621582</v>
+        <v>52.22898864746094</v>
       </c>
       <c r="C152" t="n">
         <v>64.08999633789062</v>
@@ -4406,7 +4406,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>59.23402786254883</v>
+        <v>59.23403549194336</v>
       </c>
       <c r="C154" t="n">
         <v>72.02999877929688</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>51.71773529052734</v>
+        <v>51.71774291992188</v>
       </c>
       <c r="C155" t="n">
         <v>62.88999938964844</v>
@@ -4460,7 +4460,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>47.91025543212891</v>
+        <v>47.91025161743164</v>
       </c>
       <c r="C156" t="n">
         <v>58.2599983215332</v>
@@ -4487,7 +4487,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>47.30815124511719</v>
+        <v>47.30814361572266</v>
       </c>
       <c r="C157" t="n">
         <v>56.90999984741211</v>
@@ -4514,7 +4514,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>41.16499328613281</v>
+        <v>41.16498184204102</v>
       </c>
       <c r="C158" t="n">
         <v>49.52000045776367</v>
@@ -4543,7 +4543,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>44.38203430175781</v>
+        <v>44.38204574584961</v>
       </c>
       <c r="C159" t="n">
         <v>53.38999938964844</v>
@@ -4572,7 +4572,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>47.95915222167969</v>
+        <v>47.95914077758789</v>
       </c>
       <c r="C160" t="n">
         <v>57.02999877929688</v>
@@ -4601,7 +4601,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>72.43068695068359</v>
+        <v>72.4306640625</v>
       </c>
       <c r="C161" t="n">
         <v>86.12999725341797</v>
@@ -4630,7 +4630,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>56.19201278686523</v>
+        <v>56.19202423095703</v>
       </c>
       <c r="C162" t="n">
         <v>66.81999969482422</v>
@@ -4659,7 +4659,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>64.55549621582031</v>
+        <v>64.55546569824219</v>
       </c>
       <c r="C163" t="n">
         <v>76.06999969482422</v>
@@ -4775,7 +4775,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>68.80599975585938</v>
+        <v>68.80600738525391</v>
       </c>
       <c r="C167" t="n">
         <v>80.44000244140625</v>
@@ -4804,7 +4804,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>71.46620941162109</v>
+        <v>71.46619415283203</v>
       </c>
       <c r="C168" t="n">
         <v>83.55000305175781</v>
@@ -4833,7 +4833,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>76.05451965332031</v>
+        <v>76.05453491210938</v>
       </c>
       <c r="C169" t="n">
         <v>88.23000335693359</v>
@@ -4862,7 +4862,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>73.53748321533203</v>
+        <v>73.53749084472656</v>
       </c>
       <c r="C170" t="n">
         <v>85.30999755859375</v>
@@ -4920,7 +4920,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>58.77838516235352</v>
+        <v>58.77838897705078</v>
       </c>
       <c r="C172" t="n">
         <v>67.65000152587891</v>
@@ -4978,7 +4978,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>70.27339935302734</v>
+        <v>70.27339172363281</v>
       </c>
       <c r="C174" t="n">
         <v>80.87999725341797</v>
@@ -5007,7 +5007,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>79.86207580566406</v>
+        <v>79.86209869384766</v>
       </c>
       <c r="C175" t="n">
         <v>91.20999908447266</v>
@@ -5036,7 +5036,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>92.47054290771484</v>
+        <v>92.47052001953125</v>
       </c>
       <c r="C176" t="n">
         <v>105.6100006103516</v>
@@ -5065,7 +5065,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>104.2821578979492</v>
+        <v>104.2821502685547</v>
       </c>
       <c r="C177" t="n">
         <v>119.0999984741211</v>
@@ -5094,7 +5094,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>103.5906982421875</v>
+        <v>103.5907135009766</v>
       </c>
       <c r="C178" t="n">
         <v>117.6800003051758</v>
@@ -5123,7 +5123,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>108.5906600952148</v>
+        <v>108.5906524658203</v>
       </c>
       <c r="C179" t="n">
         <v>123.3600006103516</v>
@@ -5181,7 +5181,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>134.6797943115234</v>
+        <v>134.6797790527344</v>
       </c>
       <c r="C181" t="n">
         <v>152.3399963378906</v>
@@ -5239,7 +5239,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>120.4020080566406</v>
+        <v>120.4019622802734</v>
       </c>
       <c r="C183" t="n">
         <v>136.1900024414062</v>
@@ -5268,7 +5268,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>117.7779312133789</v>
+        <v>117.7779769897461</v>
       </c>
       <c r="C184" t="n">
         <v>132.5899963378906</v>
@@ -5297,7 +5297,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>123.2942047119141</v>
+        <v>123.2942504882812</v>
       </c>
       <c r="C185" t="n">
         <v>138.8000030517578</v>
@@ -5326,7 +5326,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>119.5101165771484</v>
+        <v>119.510124206543</v>
       </c>
       <c r="C186" t="n">
         <v>134.5399932861328</v>
@@ -5355,7 +5355,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>127.6107330322266</v>
+        <v>127.610710144043</v>
       </c>
       <c r="C187" t="n">
         <v>142.9299926757812</v>
@@ -5384,7 +5384,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>133.7444152832031</v>
+        <v>133.7443542480469</v>
       </c>
       <c r="C188" t="n">
         <v>149.8000030517578</v>
@@ -5471,7 +5471,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>119.3338851928711</v>
+        <v>119.3338928222656</v>
       </c>
       <c r="C191" t="n">
         <v>133.0399932861328</v>
@@ -5529,7 +5529,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>164.6504211425781</v>
+        <v>164.650390625</v>
       </c>
       <c r="C193" t="n">
         <v>182.8699951171875</v>
@@ -5616,7 +5616,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>138.1683044433594</v>
+        <v>138.1682739257812</v>
       </c>
       <c r="C196" t="n">
         <v>152.8200073242188</v>
@@ -5645,7 +5645,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>126.297119140625</v>
+        <v>126.2971649169922</v>
       </c>
       <c r="C197" t="n">
         <v>139.6900024414062</v>
@@ -5674,7 +5674,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>129.4886932373047</v>
+        <v>129.4886779785156</v>
       </c>
       <c r="C198" t="n">
         <v>143.2200012207031</v>
@@ -5703,7 +5703,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>116.100830078125</v>
+        <v>116.1008377075195</v>
       </c>
       <c r="C199" t="n">
         <v>127.7399978637695</v>
@@ -5732,7 +5732,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>131.8427429199219</v>
+        <v>131.8427276611328</v>
       </c>
       <c r="C200" t="n">
         <v>145.0599975585938</v>
@@ -5761,7 +5761,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>120.8926696777344</v>
+        <v>120.8926620483398</v>
       </c>
       <c r="C201" t="n">
         <v>132.2700042724609</v>
@@ -5848,7 +5848,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>116.3469696044922</v>
+        <v>116.3469543457031</v>
       </c>
       <c r="C204" t="n">
         <v>126.4899978637695</v>
@@ -5877,7 +5877,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>101.1240692138672</v>
+        <v>101.1240997314453</v>
       </c>
       <c r="C205" t="n">
         <v>109.9400024414062</v>
@@ -5906,7 +5906,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>122.5280990600586</v>
+        <v>122.5280914306641</v>
       </c>
       <c r="C206" t="n">
         <v>133.2100067138672</v>
@@ -5935,7 +5935,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>113.6243209838867</v>
+        <v>113.6243133544922</v>
       </c>
       <c r="C207" t="n">
         <v>123.5299987792969</v>
@@ -5964,7 +5964,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>118.0663757324219</v>
+        <v>118.0663833618164</v>
       </c>
       <c r="C208" t="n">
         <v>127.5800018310547</v>
@@ -5993,7 +5993,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>108.0902404785156</v>
+        <v>108.0902481079102</v>
       </c>
       <c r="C209" t="n">
         <v>116.8000030517578</v>
@@ -6022,7 +6022,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>105.6818923950195</v>
+        <v>105.6818695068359</v>
       </c>
       <c r="C210" t="n">
         <v>113.4100036621094</v>
@@ -6109,7 +6109,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>107.4812622070312</v>
+        <v>107.4812698364258</v>
       </c>
       <c r="C213" t="n">
         <v>114.5299987792969</v>
@@ -6138,7 +6138,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>104.2248229980469</v>
+        <v>104.2248306274414</v>
       </c>
       <c r="C214" t="n">
         <v>111.0599975585938</v>
@@ -6167,7 +6167,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>102.2822113037109</v>
+        <v>102.2822189331055</v>
       </c>
       <c r="C215" t="n">
         <v>108.9899978637695</v>
@@ -6196,7 +6196,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>121.8778686523438</v>
+        <v>121.8778457641602</v>
       </c>
       <c r="C216" t="n">
         <v>129.0500030517578</v>
@@ -6225,7 +6225,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>136.5919494628906</v>
+        <v>136.5919799804688</v>
       </c>
       <c r="C217" t="n">
         <v>144.6300048828125</v>
@@ -6254,7 +6254,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>140.2563323974609</v>
+        <v>140.2563018798828</v>
       </c>
       <c r="C218" t="n">
         <v>148.5099945068359</v>
@@ -6283,7 +6283,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>149.7774963378906</v>
+        <v>149.7775115966797</v>
       </c>
       <c r="C219" t="n">
         <v>157.7899932861328</v>
@@ -6341,7 +6341,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>157.4282684326172</v>
+        <v>157.4282531738281</v>
       </c>
       <c r="C221" t="n">
         <v>165.8500061035156</v>
@@ -6399,7 +6399,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>189.8405914306641</v>
+        <v>189.840576171875</v>
       </c>
       <c r="C223" t="n">
         <v>199.1799926757812</v>
@@ -6457,7 +6457,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>167.0803070068359</v>
+        <v>167.0802764892578</v>
       </c>
       <c r="C225" t="n">
         <v>175.3000030517578</v>
@@ -6486,7 +6486,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>162.9140625</v>
+        <v>162.9140472412109</v>
       </c>
       <c r="C226" t="n">
         <v>170.0500030517578</v>
@@ -6515,7 +6515,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>155.9395599365234</v>
+        <v>155.9395446777344</v>
       </c>
       <c r="C227" t="n">
         <v>162.7700042724609</v>
@@ -6544,7 +6544,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>151.8774566650391</v>
+        <v>151.8774719238281</v>
       </c>
       <c r="C228" t="n">
         <v>158.5299987792969</v>
@@ -6573,7 +6573,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>147.9434051513672</v>
+        <v>147.9433746337891</v>
       </c>
       <c r="C229" t="n">
         <v>153.6199951171875</v>
@@ -6602,7 +6602,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>166.5398101806641</v>
+        <v>166.5398254394531</v>
       </c>
       <c r="C230" t="n">
         <v>172.9299926757812</v>
@@ -6631,7 +6631,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>151.3622131347656</v>
+        <v>151.3622283935547</v>
       </c>
       <c r="C231" t="n">
         <v>157.1699981689453</v>
@@ -6660,7 +6660,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>148.7314300537109</v>
+        <v>148.7314147949219</v>
       </c>
       <c r="C232" t="n">
         <v>153.6100006103516</v>
@@ -6689,7 +6689,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>143.7450103759766</v>
+        <v>143.7449798583984</v>
       </c>
       <c r="C233" t="n">
         <v>148.4600067138672</v>
@@ -6718,7 +6718,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>140.5885314941406</v>
+        <v>140.5885162353516</v>
       </c>
       <c r="C234" t="n">
         <v>145.1999969482422</v>
@@ -6776,7 +6776,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>142.9525604248047</v>
+        <v>142.9525451660156</v>
       </c>
       <c r="C236" t="n">
         <v>146.7599945068359</v>
@@ -6834,7 +6834,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>162.9662628173828</v>
+        <v>162.9662475585938</v>
       </c>
       <c r="C238" t="n">
         <v>166.3600006103516</v>
@@ -6863,7 +6863,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>177.2096252441406</v>
+        <v>177.2096099853516</v>
       </c>
       <c r="C239" t="n">
         <v>180.8999938964844</v>
@@ -6892,7 +6892,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>164.6609497070312</v>
+        <v>164.6609802246094</v>
       </c>
       <c r="C240" t="n">
         <v>168.0899963378906</v>
@@ -6921,7 +6921,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>168.4167633056641</v>
+        <v>168.416748046875</v>
       </c>
       <c r="C241" t="n">
         <v>171.0500030517578</v>
@@ -7008,7 +7008,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>127.611572265625</v>
+        <v>127.6115798950195</v>
       </c>
       <c r="C244" t="n">
         <v>128.7799987792969</v>
@@ -7066,7 +7066,7 @@
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>248.7425079345703</v>
+        <v>248.7424926757812</v>
       </c>
       <c r="C246" t="n">
         <v>251.0200042724609</v>
